--- a/artfynd/A 60313-2022 artfynd.xlsx
+++ b/artfynd/A 60313-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60313-2022 artfynd.xlsx
+++ b/artfynd/A 60313-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,220 +1014,6 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>112605208</v>
-      </c>
-      <c r="B5" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>714063</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7164612</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>112605212</v>
-      </c>
-      <c r="B6" t="n">
-        <v>91044</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4366</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Hydnellum peckii</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>714077</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7164615</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
